--- a/doc/数值设定.xlsx
+++ b/doc/数值设定.xlsx
@@ -8,34 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codes\miniFM\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0356F26A-84D2-4997-B143-1E6D30A06E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094D5F15-F92D-4FE8-B34B-6BE6CD2B0185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="球员" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>能力范围</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>人数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>联赛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -361,274 +366,226 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>200</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>190</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>180</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>170</v>
       </c>
-      <c r="C5">
-        <v>1</v>
+      <c r="G5">
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>160</v>
       </c>
-      <c r="C6">
-        <v>1</v>
+      <c r="G6">
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>150</v>
       </c>
-      <c r="C7">
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>140</v>
       </c>
-      <c r="C8">
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
         <v>2</v>
       </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>130</v>
       </c>
-      <c r="C9">
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>120</v>
       </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="G10">
+      <c r="F10">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>110</v>
       </c>
-      <c r="C11">
-        <v>2</v>
+      <c r="E11">
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>4</v>
-      </c>
-      <c r="G11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>100</v>
       </c>
-      <c r="C12">
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
         <v>3</v>
       </c>
-      <c r="F12">
-        <v>4</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>90</v>
       </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="F13">
+      <c r="E13">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>80</v>
       </c>
-      <c r="C14">
-        <v>3</v>
+      <c r="D14">
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>5</v>
-      </c>
-      <c r="F14">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>70</v>
       </c>
-      <c r="C15">
-        <v>3</v>
+      <c r="D15">
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>5</v>
-      </c>
-      <c r="F15">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>60</v>
       </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-      <c r="E16">
+      <c r="D16">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>50</v>
       </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
       <c r="C17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>6</v>
-      </c>
-      <c r="E17">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>40</v>
       </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
       <c r="C18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>6</v>
-      </c>
-      <c r="E18">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>30</v>
       </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
       <c r="C19">
-        <v>5</v>
-      </c>
-      <c r="D19">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
       <c r="C20">
-        <v>5</v>
-      </c>
-      <c r="D20">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>10</v>
       </c>
+      <c r="B21">
+        <v>16</v>
+      </c>
       <c r="C21">
         <v>6</v>
       </c>
-      <c r="D21">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B22">
         <f>SUM(B2:B21)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/doc/数值设定.xlsx
+++ b/doc/数值设定.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codes\miniFM\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094D5F15-F92D-4FE8-B34B-6BE6CD2B0185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AC33F5-F460-45F0-9188-A502B8527F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5250" yWindow="1660" windowWidth="25580" windowHeight="14870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="球员" sheetId="1" r:id="rId1"/>
@@ -34,13 +34,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>能力范围</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>人数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -84,8 +92,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -366,42 +377,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="14" width="2.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>200</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>190</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="N3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>180</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>170</v>
       </c>
@@ -411,8 +455,14 @@
       <c r="H5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>160</v>
       </c>
@@ -422,16 +472,28 @@
       <c r="H6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>150</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>140</v>
       </c>
@@ -441,8 +503,14 @@
       <c r="G8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>130</v>
       </c>
@@ -452,16 +520,28 @@
       <c r="G9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>120</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>110</v>
       </c>
@@ -471,8 +551,14 @@
       <c r="F11">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>100</v>
       </c>
@@ -482,16 +568,28 @@
       <c r="F12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K12">
+        <v>4</v>
+      </c>
+      <c r="L12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>90</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>5</v>
+      </c>
+      <c r="K13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>80</v>
       </c>
@@ -501,8 +599,14 @@
       <c r="E14">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>70</v>
       </c>
@@ -512,83 +616,99 @@
       <c r="E15">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>5</v>
+      </c>
+      <c r="K15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>60</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <v>6</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>50</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <v>6</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>40</v>
       </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <v>6</v>
+      </c>
+      <c r="J18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>30</v>
       </c>
-      <c r="B19">
-        <v>4</v>
-      </c>
       <c r="C19">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
-      <c r="B20">
-        <v>8</v>
-      </c>
       <c r="C20">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>10</v>
       </c>
-      <c r="B21">
-        <v>16</v>
-      </c>
       <c r="C21">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B22">
-        <f>SUM(B2:B21)</f>
-        <v>31</v>
+      <c r="I21">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="I1:N1"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/doc/数值设定.xlsx
+++ b/doc/数值设定.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codes\miniFM\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AC33F5-F460-45F0-9188-A502B8527F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96567973-26BB-4F8A-984D-A2743F9D07A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5250" yWindow="1660" windowWidth="25580" windowHeight="14870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="410" windowWidth="25580" windowHeight="14870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="球员" sheetId="1" r:id="rId1"/>
@@ -486,6 +486,9 @@
       <c r="G7">
         <v>2</v>
       </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
       <c r="L7">
         <v>3</v>
       </c>
@@ -503,6 +506,9 @@
       <c r="G8">
         <v>2</v>
       </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
       <c r="L8">
         <v>3</v>
       </c>
@@ -520,6 +526,9 @@
       <c r="G9">
         <v>2</v>
       </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
       <c r="L9">
         <v>3</v>
       </c>
@@ -534,6 +543,12 @@
       <c r="F10">
         <v>3</v>
       </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
       <c r="K10">
         <v>4</v>
       </c>
@@ -551,6 +566,12 @@
       <c r="F11">
         <v>3</v>
       </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
       <c r="K11">
         <v>4</v>
       </c>
@@ -568,6 +589,9 @@
       <c r="F12">
         <v>3</v>
       </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
       <c r="K12">
         <v>4</v>
       </c>
@@ -582,6 +606,12 @@
       <c r="E13">
         <v>4</v>
       </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
       <c r="J13">
         <v>5</v>
       </c>
@@ -599,6 +629,9 @@
       <c r="E14">
         <v>4</v>
       </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
       <c r="J14">
         <v>5</v>
       </c>
@@ -616,6 +649,9 @@
       <c r="E15">
         <v>4</v>
       </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
       <c r="J15">
         <v>5</v>
       </c>
@@ -630,6 +666,9 @@
       <c r="D16">
         <v>5</v>
       </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
       <c r="I16">
         <v>6</v>
       </c>
@@ -647,6 +686,9 @@
       <c r="D17">
         <v>5</v>
       </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
       <c r="I17">
         <v>6</v>
       </c>
@@ -677,6 +719,9 @@
       </c>
       <c r="C19">
         <v>6</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
       </c>
       <c r="I19">
         <v>6</v>
